--- a/public/請求書テンプレ 1.xlsx
+++ b/public/請求書テンプレ 1.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\User\Desktop\order-tool\public\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{692E9E14-4618-48C7-A3AC-FB42C1725A7B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5CC9ED9F-2EBA-46CC-AF96-C979DFB37798}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="735" yWindow="735" windowWidth="15090" windowHeight="9045" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11040" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="請求書" sheetId="24" r:id="rId1"/>
@@ -37,7 +37,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="28" uniqueCount="27">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="29" uniqueCount="28">
   <si>
     <t>No</t>
     <phoneticPr fontId="1"/>
@@ -205,6 +205,16 @@
   </si>
   <si>
     <t>〒</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>登録番号：</t>
+    <rPh sb="0" eb="2">
+      <t>トウロク</t>
+    </rPh>
+    <rPh sb="2" eb="4">
+      <t>バンゴウ</t>
+    </rPh>
     <phoneticPr fontId="1"/>
   </si>
 </sst>
@@ -2591,7 +2601,7 @@
       <c r="G12" s="29"/>
       <c r="H12" s="29"/>
       <c r="I12" s="92" t="s">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="J12" s="92"/>
       <c r="K12" s="29"/>
@@ -2605,6 +2615,9 @@
       <c r="F13" s="25"/>
       <c r="G13" s="29"/>
       <c r="H13" s="29"/>
+      <c r="I13" s="92" t="s">
+        <v>25</v>
+      </c>
       <c r="J13" s="25"/>
       <c r="K13" s="31"/>
     </row>
@@ -2990,6 +3003,15 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
+</file>
+
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
 <ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="ドキュメント" ma:contentTypeID="0x0101005080BCB0184A7849A4A0FE1681F8C714" ma:contentTypeVersion="8" ma:contentTypeDescription="新しいドキュメントを作成します。" ma:contentTypeScope="" ma:versionID="b78b8d07aa65a60436408df20eace5ee">
   <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns3="bc7c1913-bbf4-42f9-adc1-8e6ef7ea73f4" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="d48fd3ba97dedc259483476b7f229460" ns3:_="">
     <xsd:import namespace="bc7c1913-bbf4-42f9-adc1-8e6ef7ea73f4"/>
@@ -3159,15 +3181,6 @@
 </ct:contentTypeSchema>
 </file>
 
-<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
-</file>
-
 <file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
 <p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
   <documentManagement/>
@@ -3175,6 +3188,14 @@
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{85AE7D62-E5EB-42B9-88F2-79606AA51ED5}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
+</file>
+
+<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{83A82B48-70F7-434F-9F62-28FE7A052A9B}">
   <ds:schemaRefs>
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/contentType"/>
@@ -3188,14 +3209,6 @@
     <ds:schemaRef ds:uri="http://purl.org/dc/elements/1.1/"/>
     <ds:schemaRef ds:uri="http://purl.org/dc/terms/"/>
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/internal/obd"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
-</file>
-
-<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{85AE7D62-E5EB-42B9-88F2-79606AA51ED5}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
 </file>
